--- a/output/pdf_financials_xlsx/BOLT.xlsx
+++ b/output/pdf_financials_xlsx/BOLT.xlsx
@@ -1929,10 +1929,10 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.325539</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.560188</v>
       </c>
     </row>
     <row r="93">
@@ -3219,7 +3219,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -3764,7 +3768,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BOLT.xlsx
+++ b/output/pdf_financials_xlsx/BOLT.xlsx
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.06966799999999999</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.088812</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>2.764133</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.06966799999999999</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.088812</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>2.764133</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.10342</v>
+        <v>0.033752</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.993117</v>
+        <v>0.904305</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2.886412</v>
+        <v>0.122279</v>
       </c>
     </row>
     <row r="49">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
@@ -3514,7 +3514,11 @@
           <t>Reclamation deposit (Note 5)</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E27" s="5" t="n">
         <v>0.165642</v>
       </c>
@@ -6521,7 +6525,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">

--- a/output/pdf_financials_xlsx/BOLT.xlsx
+++ b/output/pdf_financials_xlsx/BOLT.xlsx
@@ -1469,10 +1469,10 @@
         <v>0</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.348566</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.506225</v>
       </c>
     </row>
     <row r="65">
@@ -1514,13 +1514,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.123357</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.137542</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.118883</v>
       </c>
     </row>
     <row r="68">
@@ -5767,7 +5767,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E98" s="5" t="n">
         <v>0.250225</v>
       </c>
